--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEC01BE-8EDC-43B0-A97D-D739B00E348A}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE12CC4-5E88-4124-9414-B879B8132C87}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="4320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t xml:space="preserve">Site </t>
   </si>
@@ -47,9 +47,6 @@
     <t>Dispatcher</t>
   </si>
   <si>
-    <t>Acknowledged by</t>
-  </si>
-  <si>
     <t>Resolution</t>
   </si>
   <si>
@@ -207,6 +204,12 @@
   </si>
   <si>
     <t>Vendor</t>
+  </si>
+  <si>
+    <t>maintanenceValue</t>
+  </si>
+  <si>
+    <t>AcknowledgedBy</t>
   </si>
 </sst>
 </file>
@@ -548,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="4" width="20.47265625" customWidth="1"/>
@@ -569,37 +572,38 @@
     <col min="32" max="32" width="25" customWidth="1"/>
     <col min="33" max="33" width="12.47265625" customWidth="1"/>
     <col min="34" max="35" width="10.62890625" customWidth="1"/>
-    <col min="36" max="36" width="12.1015625" customWidth="1"/>
-    <col min="38" max="38" width="23.62890625" customWidth="1"/>
-    <col min="39" max="40" width="25.89453125" customWidth="1"/>
-    <col min="41" max="41" width="21" customWidth="1"/>
-    <col min="42" max="44" width="25.89453125" customWidth="1"/>
-    <col min="45" max="45" width="16.26171875" customWidth="1"/>
-    <col min="46" max="46" width="17" customWidth="1"/>
-    <col min="47" max="48" width="16.1015625" customWidth="1"/>
-    <col min="49" max="49" width="9.3671875" customWidth="1"/>
-    <col min="50" max="50" width="12.47265625" customWidth="1"/>
-    <col min="52" max="52" width="23.89453125" customWidth="1"/>
+    <col min="36" max="37" width="12.1015625" customWidth="1"/>
+    <col min="38" max="38" width="33.578125" customWidth="1"/>
+    <col min="39" max="39" width="23.62890625" customWidth="1"/>
+    <col min="40" max="41" width="25.89453125" customWidth="1"/>
+    <col min="42" max="42" width="21" customWidth="1"/>
+    <col min="43" max="45" width="25.89453125" customWidth="1"/>
+    <col min="46" max="46" width="16.26171875" customWidth="1"/>
+    <col min="47" max="47" width="17" customWidth="1"/>
+    <col min="48" max="49" width="16.1015625" customWidth="1"/>
+    <col min="50" max="50" width="9.3671875" customWidth="1"/>
+    <col min="51" max="51" width="12.47265625" customWidth="1"/>
+    <col min="53" max="53" width="23.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15.3">
+    <row r="1" spans="1:53" ht="15.3">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -614,133 +618,136 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AZ1" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:53">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
@@ -763,40 +770,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" t="s">
-        <v>59</v>
-      </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE12CC4-5E88-4124-9414-B879B8132C87}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7505FDA4-E6DB-411F-921B-9CA40751E589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="1830" windowWidth="22704" windowHeight="8994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t xml:space="preserve">Site </t>
   </si>
@@ -210,6 +210,14 @@
   </si>
   <si>
     <t>AcknowledgedBy</t>
+  </si>
+  <si>
+    <t>SiebleNumber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CallCenterNumber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -220,7 +228,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -233,7 +241,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -241,7 +249,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -273,7 +281,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -551,42 +559,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:BC2"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
-    <col min="2" max="4" width="20.47265625" customWidth="1"/>
-    <col min="5" max="6" width="23.1015625" customWidth="1"/>
-    <col min="7" max="7" width="16.3671875" customWidth="1"/>
-    <col min="8" max="17" width="17.47265625" customWidth="1"/>
-    <col min="18" max="18" width="20.3671875" customWidth="1"/>
-    <col min="19" max="20" width="16.26171875" customWidth="1"/>
-    <col min="21" max="21" width="15.89453125" customWidth="1"/>
-    <col min="22" max="22" width="25.3671875" customWidth="1"/>
+    <col min="2" max="4" width="20.44921875" customWidth="1"/>
+    <col min="5" max="6" width="23.09765625" customWidth="1"/>
+    <col min="7" max="7" width="16.34765625" customWidth="1"/>
+    <col min="8" max="17" width="17.44921875" customWidth="1"/>
+    <col min="18" max="18" width="20.34765625" customWidth="1"/>
+    <col min="19" max="20" width="16.25" customWidth="1"/>
+    <col min="21" max="21" width="15.8984375" customWidth="1"/>
+    <col min="22" max="22" width="25.34765625" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="14.1015625" customWidth="1"/>
-    <col min="25" max="25" width="14.62890625" customWidth="1"/>
-    <col min="26" max="26" width="26.1015625" customWidth="1"/>
+    <col min="24" max="24" width="14.09765625" customWidth="1"/>
+    <col min="25" max="25" width="14.6484375" customWidth="1"/>
+    <col min="26" max="26" width="26.09765625" customWidth="1"/>
     <col min="27" max="27" width="25" customWidth="1"/>
-    <col min="28" max="30" width="16.3671875" customWidth="1"/>
-    <col min="31" max="31" width="12.26171875" customWidth="1"/>
+    <col min="28" max="30" width="16.34765625" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
     <col min="32" max="32" width="25" customWidth="1"/>
-    <col min="33" max="33" width="12.47265625" customWidth="1"/>
-    <col min="34" max="35" width="10.62890625" customWidth="1"/>
-    <col min="36" max="37" width="12.1015625" customWidth="1"/>
-    <col min="38" max="38" width="33.578125" customWidth="1"/>
-    <col min="39" max="39" width="23.62890625" customWidth="1"/>
-    <col min="40" max="41" width="25.89453125" customWidth="1"/>
+    <col min="33" max="33" width="12.44921875" customWidth="1"/>
+    <col min="34" max="35" width="10.6484375" customWidth="1"/>
+    <col min="36" max="37" width="12.09765625" customWidth="1"/>
+    <col min="38" max="38" width="33.59765625" customWidth="1"/>
+    <col min="39" max="39" width="23.6484375" customWidth="1"/>
+    <col min="40" max="41" width="25.8984375" customWidth="1"/>
     <col min="42" max="42" width="21" customWidth="1"/>
-    <col min="43" max="45" width="25.89453125" customWidth="1"/>
-    <col min="46" max="46" width="16.26171875" customWidth="1"/>
+    <col min="43" max="45" width="25.8984375" customWidth="1"/>
+    <col min="46" max="46" width="16.25" customWidth="1"/>
     <col min="47" max="47" width="17" customWidth="1"/>
-    <col min="48" max="49" width="16.1015625" customWidth="1"/>
-    <col min="50" max="50" width="9.3671875" customWidth="1"/>
-    <col min="51" max="51" width="12.47265625" customWidth="1"/>
-    <col min="53" max="53" width="23.89453125" customWidth="1"/>
+    <col min="48" max="49" width="16.09765625" customWidth="1"/>
+    <col min="50" max="50" width="9.34765625" customWidth="1"/>
+    <col min="51" max="51" width="12.44921875" customWidth="1"/>
+    <col min="53" max="53" width="23.8984375" customWidth="1"/>
+    <col min="54" max="54" width="12.796875" customWidth="1"/>
+    <col min="55" max="55" width="11.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="15.3">
+    <row r="1" spans="1:55" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -746,8 +756,14 @@
       <c r="BA1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="BB1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:55">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
@@ -763,9 +779,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
-    <col min="3" max="3" width="10.89453125" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7505FDA4-E6DB-411F-921B-9CA40751E589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F28260-B6C8-4FE9-83CD-F3C17854F948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="1830" windowWidth="22704" windowHeight="8994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="696" windowWidth="22704" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -212,11 +212,11 @@
     <t>AcknowledgedBy</t>
   </si>
   <si>
-    <t>SiebleNumber</t>
+    <t>CallCenterNumber</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CallCenterNumber</t>
+    <t>SiebelNumber</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -757,10 +757,10 @@
         <v>8</v>
       </c>
       <c r="BB1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:55">

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F28260-B6C8-4FE9-83CD-F3C17854F948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E89F46-FE0B-4A02-B0FD-BAF70D6FB6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="696" windowWidth="22704" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t xml:space="preserve">Site </t>
   </si>
@@ -217,6 +217,14 @@
   </si>
   <si>
     <t>SiebelNumber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntryType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WorkHourDetail</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -559,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC2"/>
+  <dimension ref="A1:BE2"/>
   <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="2" max="4" width="20.44921875" customWidth="1"/>
@@ -596,7 +604,7 @@
     <col min="55" max="55" width="11.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="15.3">
+    <row r="1" spans="1:57" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -762,8 +770,14 @@
       <c r="BC1" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="BD1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="2" spans="1:55">
+    <row r="2" spans="1:57">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrder_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E89F46-FE0B-4A02-B0FD-BAF70D6FB6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2C699C-B66F-4A54-9F3E-F1E0C996E819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrder List" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t xml:space="preserve">Site </t>
   </si>
@@ -226,6 +226,15 @@
   <si>
     <t>WorkHourDetail</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoworkerEntryType</t>
+  </si>
+  <si>
+    <t>CoworkerEntryDetail</t>
+  </si>
+  <si>
+    <t>WorkOrderType</t>
   </si>
 </sst>
 </file>
@@ -236,7 +245,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -249,7 +258,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -257,7 +266,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -567,44 +576,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE2"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <dimension ref="A1:BH2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="4" width="20.44921875" customWidth="1"/>
-    <col min="5" max="6" width="23.09765625" customWidth="1"/>
-    <col min="7" max="7" width="16.34765625" customWidth="1"/>
-    <col min="8" max="17" width="17.44921875" customWidth="1"/>
-    <col min="18" max="18" width="20.34765625" customWidth="1"/>
-    <col min="19" max="20" width="16.25" customWidth="1"/>
-    <col min="21" max="21" width="15.8984375" customWidth="1"/>
-    <col min="22" max="22" width="25.34765625" customWidth="1"/>
+    <col min="2" max="4" width="20.41796875" customWidth="1"/>
+    <col min="5" max="6" width="23.1015625" customWidth="1"/>
+    <col min="7" max="7" width="16.3671875" customWidth="1"/>
+    <col min="8" max="17" width="17.41796875" customWidth="1"/>
+    <col min="18" max="18" width="20.3671875" customWidth="1"/>
+    <col min="19" max="20" width="16.26171875" customWidth="1"/>
+    <col min="21" max="21" width="15.89453125" customWidth="1"/>
+    <col min="22" max="22" width="25.3671875" customWidth="1"/>
     <col min="23" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="14.09765625" customWidth="1"/>
-    <col min="25" max="25" width="14.6484375" customWidth="1"/>
-    <col min="26" max="26" width="26.09765625" customWidth="1"/>
+    <col min="24" max="24" width="14.1015625" customWidth="1"/>
+    <col min="25" max="25" width="14.62890625" customWidth="1"/>
+    <col min="26" max="26" width="26.1015625" customWidth="1"/>
     <col min="27" max="27" width="25" customWidth="1"/>
-    <col min="28" max="30" width="16.34765625" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="28" max="30" width="16.3671875" customWidth="1"/>
+    <col min="31" max="31" width="12.26171875" customWidth="1"/>
     <col min="32" max="32" width="25" customWidth="1"/>
-    <col min="33" max="33" width="12.44921875" customWidth="1"/>
-    <col min="34" max="35" width="10.6484375" customWidth="1"/>
-    <col min="36" max="37" width="12.09765625" customWidth="1"/>
-    <col min="38" max="38" width="33.59765625" customWidth="1"/>
-    <col min="39" max="39" width="23.6484375" customWidth="1"/>
-    <col min="40" max="41" width="25.8984375" customWidth="1"/>
+    <col min="33" max="33" width="12.41796875" customWidth="1"/>
+    <col min="34" max="35" width="10.62890625" customWidth="1"/>
+    <col min="36" max="37" width="12.1015625" customWidth="1"/>
+    <col min="38" max="38" width="33.578125" customWidth="1"/>
+    <col min="39" max="39" width="23.62890625" customWidth="1"/>
+    <col min="40" max="41" width="25.89453125" customWidth="1"/>
     <col min="42" max="42" width="21" customWidth="1"/>
-    <col min="43" max="45" width="25.8984375" customWidth="1"/>
-    <col min="46" max="46" width="16.25" customWidth="1"/>
+    <col min="43" max="45" width="25.89453125" customWidth="1"/>
+    <col min="46" max="46" width="16.26171875" customWidth="1"/>
     <col min="47" max="47" width="17" customWidth="1"/>
-    <col min="48" max="49" width="16.09765625" customWidth="1"/>
-    <col min="50" max="50" width="9.34765625" customWidth="1"/>
-    <col min="51" max="51" width="12.44921875" customWidth="1"/>
-    <col min="53" max="53" width="23.8984375" customWidth="1"/>
-    <col min="54" max="54" width="12.796875" customWidth="1"/>
-    <col min="55" max="55" width="11.69921875" customWidth="1"/>
+    <col min="48" max="49" width="16.1015625" customWidth="1"/>
+    <col min="50" max="50" width="9.3671875" customWidth="1"/>
+    <col min="51" max="51" width="12.41796875" customWidth="1"/>
+    <col min="53" max="53" width="23.89453125" customWidth="1"/>
+    <col min="54" max="54" width="12.7890625" customWidth="1"/>
+    <col min="55" max="55" width="11.68359375" customWidth="1"/>
+    <col min="56" max="56" width="14.734375" customWidth="1"/>
+    <col min="57" max="57" width="18.89453125" customWidth="1"/>
+    <col min="58" max="58" width="19.9453125" customWidth="1"/>
+    <col min="59" max="59" width="25.89453125" customWidth="1"/>
+    <col min="60" max="60" width="24.05078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="15.3">
+    <row r="1" spans="1:60" ht="15.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -776,8 +790,17 @@
       <c r="BE1" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="BF1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:57">
+    <row r="2" spans="1:60">
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
@@ -793,9 +816,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B27B56-1823-4D07-9234-02F082420C5C}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="10.8984375" customWidth="1"/>
+    <col min="3" max="3" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
